--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY686"/>
+  <dimension ref="A1:AZ686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128289620</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457603</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98945669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338506</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851758</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128289026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115145594</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128289913</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111127195</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118490950</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123708279</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86496254</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2074,6 +2139,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100251895</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337640</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214612</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2391,6 +2471,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103903111</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2492,6 +2577,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214571</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2606,6 +2696,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111182677</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2721,6 +2816,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252562</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457646</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2936,6 +3041,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131694354</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3043,6 +3153,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103903001</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3148,6 +3263,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127932235</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3278,6 +3398,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061120</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3414,6 +3539,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061121</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3550,6 +3680,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061123</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3686,6 +3821,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061124</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3822,6 +3962,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061125</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3958,6 +4103,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061126</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4085,6 +4235,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061127</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4212,6 +4367,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061128</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4339,6 +4499,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061129</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4466,6 +4631,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061119</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4587,6 +4757,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061131</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4694,6 +4869,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115953772</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4801,6 +4981,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061117</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4911,6 +5096,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252030</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5021,6 +5211,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252080</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5122,6 +5317,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214787</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5223,6 +5423,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214830</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5329,6 +5534,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119061006</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5444,6 +5654,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929399</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5559,6 +5774,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929483</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5675,6 +5895,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929535</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5786,6 +6011,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122928987</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5897,6 +6127,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929342</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6004,6 +6239,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859625</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6111,6 +6351,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859619</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6217,6 +6462,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113689593</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6323,6 +6573,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563617</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6429,6 +6684,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563797</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6535,6 +6795,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563832</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6641,6 +6906,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564415</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6742,6 +7012,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129565002</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6843,6 +7118,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104247939</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6944,6 +7224,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214713</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7045,6 +7330,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128886693</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7152,6 +7442,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859620</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7253,6 +7548,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122435803</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7380,6 +7680,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859626</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7481,6 +7786,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457948</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7582,6 +7892,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457964</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7683,6 +7998,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564997</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7784,6 +8104,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230377</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7885,6 +8210,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128886665</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7986,6 +8316,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342127</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8087,6 +8422,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457671</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8188,6 +8528,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457697</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8289,6 +8634,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457938</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8395,6 +8745,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591415</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8515,6 +8870,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859622</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8622,6 +8982,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134100841</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8754,6 +9119,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859623</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8859,6 +9229,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128510434</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8964,6 +9339,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591579</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9069,6 +9449,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133115563</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9171,6 +9556,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564285</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9272,6 +9662,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564006</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9382,6 +9777,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843519</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9487,6 +9887,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87738455</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9596,6 +10001,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131834055</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9710,6 +10120,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135075557</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9826,6 +10241,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115953594</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9937,6 +10357,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930166</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10052,6 +10477,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491342</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10167,6 +10597,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491392</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10268,6 +10703,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564253</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10375,6 +10815,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061106</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10476,6 +10921,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119060941</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10590,6 +11040,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545619</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10701,6 +11156,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930205</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10808,6 +11268,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061107</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10915,6 +11380,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061114</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11016,6 +11486,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215187</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11122,6 +11597,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342170</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11233,6 +11713,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643445</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11339,6 +11824,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591650</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11448,6 +11938,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342241</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11575,6 +12070,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061104</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11702,6 +12202,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061087</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11829,6 +12334,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11934,6 +12444,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491267</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12039,6 +12554,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844041</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12149,6 +12669,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127932257</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12258,6 +12783,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132843438</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12367,6 +12897,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132843512</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12494,6 +13029,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061088</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12621,6 +13161,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061109</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12757,6 +13302,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12879,6 +13429,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061105</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12995,6 +13550,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061089</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13102,6 +13662,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061098</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13223,6 +13788,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061108</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13325,6 +13895,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117554483</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13432,6 +14007,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061091</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13539,6 +14119,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061099</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13646,6 +14231,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061102</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13756,6 +14346,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234644</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13872,6 +14467,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061092</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13988,6 +14588,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061094</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14104,6 +14709,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061100</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14211,6 +14821,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89471011</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14308,6 +14923,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121742517</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14419,6 +15039,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930294</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14516,6 +15141,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125963374</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14623,6 +15253,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061090</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14730,6 +15365,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061103</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14836,6 +15476,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672171</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14953,6 +15598,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240952</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15069,6 +15719,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813868</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15175,6 +15830,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337741</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15302,6 +15962,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859633</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15416,6 +16081,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122220670</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15522,6 +16192,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89470832</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15623,6 +16298,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89470860</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15729,6 +16409,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564096</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15835,6 +16520,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564502</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15941,6 +16631,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564524</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16042,6 +16737,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592095</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16149,6 +16849,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859636</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16254,6 +16959,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457812</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16355,6 +17065,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89470845</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16456,6 +17171,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96458425</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16564,6 +17284,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240523</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16681,6 +17406,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97241458</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16808,6 +17538,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859630</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16935,6 +17670,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859632</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17041,6 +17781,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564176</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17151,6 +17896,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564462</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17252,6 +18002,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591539</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17353,6 +18108,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591551</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17454,6 +18214,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96858751</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17577,6 +18342,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239630</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17678,6 +18448,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342050</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17779,6 +18554,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457830</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17880,6 +18660,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457855</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17981,6 +18766,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457880</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18082,6 +18872,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128510579</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18183,6 +18978,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646813</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18288,6 +19088,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337759</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18394,6 +19199,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94982629</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18500,6 +19310,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643401</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18613,6 +19428,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239870</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18736,6 +19556,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240368</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18844,6 +19669,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97241125</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18954,6 +19784,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592077</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19055,6 +19890,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643356</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19171,6 +20011,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239536</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19287,6 +20132,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813853</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19414,6 +20264,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859628</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19530,6 +20385,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813854</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19639,6 +20499,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215212</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19749,6 +20614,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240536</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19863,6 +20733,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779133</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19995,6 +20870,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239700</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20122,6 +21002,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859634</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20231,6 +21116,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234616</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20336,6 +21226,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128886960</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20458,6 +21353,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859629</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20580,6 +21480,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859631</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20707,6 +21612,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061086</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20813,6 +21723,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126233785</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20927,6 +21842,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234439</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21037,6 +21957,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234771</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21139,6 +22064,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890506</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21246,6 +22176,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859637</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21353,6 +22288,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122781008</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21455,6 +22395,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126003574</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21565,6 +22510,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234373</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21662,6 +22612,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116746465</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21769,6 +22724,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125976418</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21883,6 +22843,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234400</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21994,6 +22959,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487656</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22096,6 +23066,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116757706</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22208,6 +23183,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859651</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22309,6 +23289,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215511</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22415,6 +23400,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736615</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22523,6 +23513,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242271</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22631,6 +23626,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242371</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22732,6 +23732,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230409</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22840,6 +23845,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97241880</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22947,6 +23957,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418797</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23057,6 +24072,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122988731</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23162,6 +24182,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230389</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23269,6 +24294,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111182876</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23371,6 +24401,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133767702</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23490,6 +24525,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86686018</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23592,6 +24632,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672256</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23701,6 +24746,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242656</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23810,6 +24860,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97243108</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23930,6 +24985,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330311</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24045,6 +25105,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98104097</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24155,6 +25220,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119475594</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24262,6 +25332,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859638</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24369,6 +25444,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859639</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24476,6 +25556,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859640</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24592,6 +25677,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859642</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24699,6 +25789,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859643</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24806,6 +25901,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859644</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24913,6 +26013,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859646</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25020,6 +26125,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859647</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25127,6 +26237,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859649</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25234,6 +26349,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859650</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25349,6 +26469,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418709</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25464,6 +26589,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418756</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25566,6 +26696,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128510717</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25668,6 +26803,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133767721</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25787,6 +26927,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95668898</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25906,6 +27051,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102184454</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26030,6 +27180,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17034325</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26149,6 +27304,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92259685</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26260,6 +27420,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87166814</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26375,6 +27540,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491001</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26495,6 +27665,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135075195</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26610,6 +27785,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102521118</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26725,6 +27905,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118490853</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26822,6 +28007,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125966818</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26929,6 +28119,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004296</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27026,6 +28221,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126478431</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27136,6 +28336,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100669530</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27246,6 +28451,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100669601</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27377,6 +28587,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061113</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27478,6 +28693,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342188</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27579,6 +28799,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672381</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27680,6 +28905,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646771</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27785,6 +29015,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135074047</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27890,6 +29125,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646792</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28001,6 +29241,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491534</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28108,6 +29353,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204547</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28215,6 +29465,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104249959</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28330,6 +29585,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122220583</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28432,6 +29692,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94296788</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28534,6 +29799,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204577</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28636,6 +29906,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100669619</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28743,6 +30018,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061111</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28850,6 +30130,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061110</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28956,6 +30241,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564577</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29062,6 +30352,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592113</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29169,6 +30464,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859657</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29289,6 +30589,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129263411</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29408,6 +30713,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129263302</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29509,6 +30819,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672273</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29610,6 +30925,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564587</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29711,6 +31031,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592228</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29812,6 +31137,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215443</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29913,6 +31243,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564547</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -30027,6 +31362,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129263646</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30128,6 +31468,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128886978</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30229,6 +31574,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252349</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30330,6 +31680,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672335</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30431,6 +31786,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564941</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30545,6 +31905,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779186</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30659,6 +32024,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779241</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30764,6 +32134,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118809291</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30865,6 +32240,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123368623</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30970,6 +32350,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491426</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31075,6 +32460,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564703</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31180,6 +32570,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592259</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31285,6 +32680,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134505793</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31412,6 +32812,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859656</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31519,6 +32924,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131936272</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31630,6 +33040,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128095464</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31742,6 +33157,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488564</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31863,6 +33283,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061081</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31965,6 +33390,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126005160</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32072,6 +33502,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061084</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32178,6 +33613,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234010</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32285,6 +33725,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96858761</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32382,6 +33827,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116743172</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32479,6 +33929,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125965889</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32586,6 +34041,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061078</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32693,6 +34153,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061079</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32807,6 +34272,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234937</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32914,6 +34384,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061082</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33041,6 +34516,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859655</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33156,6 +34636,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211837</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33266,6 +34751,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212021</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33381,6 +34871,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212066</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33496,6 +34991,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212101</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -33611,6 +35111,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212143</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -33712,6 +35217,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399185</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -33818,6 +35328,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736772</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33919,6 +35434,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129192275</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34020,6 +35540,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212708</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34121,6 +35646,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215334</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34222,6 +35752,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399160</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -34323,6 +35858,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457904</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34431,6 +35971,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242116</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -34532,6 +36077,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457920</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -34634,6 +36184,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73768473</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -34740,6 +36295,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672230</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -34846,6 +36406,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103354390</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -34952,6 +36517,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337965</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35074,6 +36644,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859654</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35179,6 +36754,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122778162</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35297,6 +36877,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779259</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35402,6 +36987,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491496</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -35507,6 +37097,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215416</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -35612,6 +37207,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135546260</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -35723,6 +37323,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128510952</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -35830,6 +37435,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124721625</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -35932,6 +37542,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126003792</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36034,6 +37649,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004064</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36145,6 +37765,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234159</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36256,6 +37881,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487814</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -36363,6 +37993,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211661</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -36478,6 +38113,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211902</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -36588,6 +38228,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212209</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -36703,6 +38348,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127932426</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -36813,6 +38463,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341941</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -36915,6 +38570,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94982809</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37017,6 +38677,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643458</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37119,6 +38784,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252927</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37226,6 +38896,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859660</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -37328,6 +39003,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124593593</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -37430,6 +39110,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004025</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -37545,6 +39230,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643468</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -37656,6 +39346,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192342</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -37768,6 +39463,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859678</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -37870,6 +39570,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101523203</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -37976,6 +39681,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117554655</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -38087,6 +39797,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487623</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -38198,6 +39913,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487957</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -38309,6 +40029,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -38424,6 +40149,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004335</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -38539,6 +40269,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212243</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -38640,6 +40375,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399092</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -38745,6 +40485,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111177152</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -38846,6 +40591,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399072</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -38956,6 +40706,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211482</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39066,6 +40821,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211545</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -39168,6 +40928,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519751</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -39270,6 +41035,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004216</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -39372,6 +41142,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004260</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -39474,6 +41249,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004295</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -39581,6 +41361,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78194577</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -39688,6 +41473,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859680</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -39795,6 +41585,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859681</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -39902,6 +41697,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859679</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40009,6 +41809,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859683</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -40116,6 +41921,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859682</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -40239,6 +42049,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129270144</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -40341,6 +42156,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94982679</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -40460,6 +42280,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95124090</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -40584,6 +42409,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102183381</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -40708,6 +42538,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102183427</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -40818,6 +42653,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102316114</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -40937,6 +42777,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110471482</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41056,6 +42901,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110687467</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -41175,6 +43025,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110687587</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -41294,6 +43149,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110687716</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -41413,6 +43273,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88132036</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -41535,6 +43400,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122657455</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -41636,6 +43506,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96086466</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -41754,6 +43629,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102183453</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -41863,6 +43743,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152950</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -41973,6 +43858,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131833931</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -42082,6 +43972,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131936172</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -42189,6 +44084,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117710851</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -42295,6 +44195,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487433</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -42401,6 +44306,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487523</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -42507,6 +44417,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487474</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -42608,6 +44523,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646976</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -42714,6 +44634,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647386</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -42820,6 +44745,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647535</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -42921,6 +44851,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647736</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -43022,6 +44957,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647775</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -43123,6 +45063,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647797</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -43229,6 +45174,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952147</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -43330,6 +45280,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337971</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -43431,6 +45386,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337999</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -43532,6 +45492,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952421</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -43633,6 +45598,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952343</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -43734,6 +45704,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338493</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -43835,6 +45810,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952231</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -43936,6 +45916,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337992</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -44037,6 +46022,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337980</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -44138,6 +46128,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952392</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -44253,6 +46248,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129261904</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -44354,6 +46354,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952217</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -44460,6 +46465,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128290148</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -44561,6 +46571,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91020515</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -44662,6 +46677,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645932</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -44763,6 +46783,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952372</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -44868,6 +46893,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128289937</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -44977,6 +47007,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128290019</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -45078,6 +47113,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646670</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -45179,6 +47219,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646681</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -45280,6 +47325,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646698</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -45381,6 +47431,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646716</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -45482,6 +47537,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967540</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -45583,6 +47643,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338009</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -45689,6 +47754,11 @@
         </is>
       </c>
       <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952123</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -45790,6 +47860,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95743032</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -45895,6 +47970,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128090311</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -46000,6 +48080,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647365</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -46101,6 +48186,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626320</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -46202,6 +48292,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626357</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -46303,6 +48398,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647453</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -46404,6 +48504,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887322</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -46505,6 +48610,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887372</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -46606,6 +48716,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952311</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -46707,6 +48822,11 @@
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952321</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -46808,6 +48928,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887282</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -46913,6 +49038,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359246</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -47014,6 +49144,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319687</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -47120,6 +49255,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527150</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -47221,6 +49361,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319692</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -47322,6 +49467,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118809322</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -47423,6 +49573,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128315352</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -47524,6 +49679,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317394</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -47625,6 +49785,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952287</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -47726,6 +49891,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128089929</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -47827,6 +49997,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128089976</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -47928,6 +50103,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887397</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -48038,6 +50218,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128090057</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -48139,6 +50324,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887356</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -48245,6 +50435,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626296</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -48346,6 +50541,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645852</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -48447,6 +50647,11 @@
         </is>
       </c>
       <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128359370</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -48548,6 +50753,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527290</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -48649,6 +50859,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887307</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -48750,6 +50965,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527113</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -48851,6 +51071,11 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527258</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -48961,6 +51186,11 @@
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129262153</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -49076,6 +51306,11 @@
         </is>
       </c>
       <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129262983</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -49186,6 +51421,11 @@
         </is>
       </c>
       <c r="AY448" t="inlineStr"/>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129263731</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -49296,6 +51536,11 @@
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624935</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -49410,6 +51655,11 @@
         </is>
       </c>
       <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779249</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -49524,6 +51774,11 @@
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779251</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -49629,6 +51884,11 @@
         </is>
       </c>
       <c r="AY452" t="inlineStr"/>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123014554</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -49734,6 +51994,11 @@
         </is>
       </c>
       <c r="AY453" t="inlineStr"/>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952275</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -49841,6 +52106,11 @@
         </is>
       </c>
       <c r="AY454" t="inlineStr"/>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129647413</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -49953,6 +52223,11 @@
         </is>
       </c>
       <c r="AY455" t="inlineStr"/>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126770456</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -50056,6 +52331,11 @@
         </is>
       </c>
       <c r="AY456" t="inlineStr"/>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887206</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -50159,6 +52439,11 @@
         </is>
       </c>
       <c r="AY457" t="inlineStr"/>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952057</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -50261,6 +52546,11 @@
         </is>
       </c>
       <c r="AY458" t="inlineStr"/>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126005099</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -50372,6 +52662,11 @@
         </is>
       </c>
       <c r="AY459" t="inlineStr"/>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129262166</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -50479,6 +52774,11 @@
         </is>
       </c>
       <c r="AY460" t="inlineStr"/>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859666</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -50580,6 +52880,11 @@
         </is>
       </c>
       <c r="AY461" t="inlineStr"/>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398269</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -50686,6 +52991,11 @@
         </is>
       </c>
       <c r="AY462" t="inlineStr"/>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968276</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -50792,6 +53102,11 @@
         </is>
       </c>
       <c r="AY463" t="inlineStr"/>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592411</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -50898,6 +53213,11 @@
         </is>
       </c>
       <c r="AY464" t="inlineStr"/>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592461</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -50999,6 +53319,11 @@
         </is>
       </c>
       <c r="AY465" t="inlineStr"/>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626491</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -51100,6 +53425,11 @@
         </is>
       </c>
       <c r="AY466" t="inlineStr"/>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626506</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -51201,6 +53531,11 @@
         </is>
       </c>
       <c r="AY467" t="inlineStr"/>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736828</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -51302,6 +53637,11 @@
         </is>
       </c>
       <c r="AY468" t="inlineStr"/>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736849</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -51403,6 +53743,11 @@
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968375</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -51504,6 +53849,11 @@
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398408</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -51611,6 +53961,11 @@
         </is>
       </c>
       <c r="AY471" t="inlineStr"/>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859662</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -51712,6 +54067,11 @@
         </is>
       </c>
       <c r="AY472" t="inlineStr"/>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492249</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -51813,6 +54173,11 @@
         </is>
       </c>
       <c r="AY473" t="inlineStr"/>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319674</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -51914,6 +54279,11 @@
         </is>
       </c>
       <c r="AY474" t="inlineStr"/>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968317</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -52015,6 +54385,11 @@
         </is>
       </c>
       <c r="AY475" t="inlineStr"/>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128089920</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -52116,6 +54491,11 @@
         </is>
       </c>
       <c r="AY476" t="inlineStr"/>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968223</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -52217,6 +54597,11 @@
         </is>
       </c>
       <c r="AY477" t="inlineStr"/>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626405</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -52318,6 +54703,11 @@
         </is>
       </c>
       <c r="AY478" t="inlineStr"/>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519747</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -52419,6 +54809,11 @@
         </is>
       </c>
       <c r="AY479" t="inlineStr"/>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646833</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -52525,6 +54920,11 @@
         </is>
       </c>
       <c r="AY480" t="inlineStr"/>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887180</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -52626,6 +55026,11 @@
         </is>
       </c>
       <c r="AY481" t="inlineStr"/>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968248</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -52727,6 +55132,11 @@
         </is>
       </c>
       <c r="AY482" t="inlineStr"/>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646827</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -52836,6 +55246,11 @@
         </is>
       </c>
       <c r="AY483" t="inlineStr"/>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341914</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -52941,6 +55356,11 @@
         </is>
       </c>
       <c r="AY484" t="inlineStr"/>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124593051</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -53046,6 +55466,11 @@
         </is>
       </c>
       <c r="AY485" t="inlineStr"/>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127431864</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -53151,6 +55576,11 @@
         </is>
       </c>
       <c r="AY486" t="inlineStr"/>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341890</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -53256,6 +55686,11 @@
         </is>
       </c>
       <c r="AY487" t="inlineStr"/>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736793</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -53359,6 +55794,11 @@
         </is>
       </c>
       <c r="AY488" t="inlineStr"/>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736810</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -53461,6 +55901,11 @@
         </is>
       </c>
       <c r="AY489" t="inlineStr"/>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004805</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -53563,6 +56008,11 @@
         </is>
       </c>
       <c r="AY490" t="inlineStr"/>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004817</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -53670,6 +56120,11 @@
         </is>
       </c>
       <c r="AY491" t="inlineStr"/>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859669</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -53772,6 +56227,11 @@
         </is>
       </c>
       <c r="AY492" t="inlineStr"/>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111689384</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -53879,6 +56339,11 @@
         </is>
       </c>
       <c r="AY493" t="inlineStr"/>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859661</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -53986,6 +56451,11 @@
         </is>
       </c>
       <c r="AY494" t="inlineStr"/>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859668</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -54093,6 +56563,11 @@
         </is>
       </c>
       <c r="AY495" t="inlineStr"/>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126079502</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -54195,6 +56670,11 @@
         </is>
       </c>
       <c r="AY496" t="inlineStr"/>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131694769</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -54309,6 +56789,11 @@
         </is>
       </c>
       <c r="AY497" t="inlineStr"/>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234839</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -54423,6 +56908,11 @@
         </is>
       </c>
       <c r="AY498" t="inlineStr"/>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234886</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -54524,6 +57014,11 @@
         </is>
       </c>
       <c r="AY499" t="inlineStr"/>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968424</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -54631,6 +57126,11 @@
         </is>
       </c>
       <c r="AY500" t="inlineStr"/>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859675</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -54738,6 +57238,11 @@
         </is>
       </c>
       <c r="AY501" t="inlineStr"/>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859677</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -54848,6 +57353,11 @@
         </is>
       </c>
       <c r="AY502" t="inlineStr"/>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101523335</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -54963,6 +57473,11 @@
         </is>
       </c>
       <c r="AY503" t="inlineStr"/>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004158</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -55064,6 +57579,11 @@
         </is>
       </c>
       <c r="AY504" t="inlineStr"/>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398950</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -55165,6 +57685,11 @@
         </is>
       </c>
       <c r="AY505" t="inlineStr"/>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230567</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -55266,6 +57791,11 @@
         </is>
       </c>
       <c r="AY506" t="inlineStr"/>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230467</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -55372,6 +57902,11 @@
         </is>
       </c>
       <c r="AY507" t="inlineStr"/>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492337</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -55473,6 +58008,11 @@
         </is>
       </c>
       <c r="AY508" t="inlineStr"/>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398912</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -55574,6 +58114,11 @@
         </is>
       </c>
       <c r="AY509" t="inlineStr"/>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398945</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -55676,6 +58221,11 @@
         </is>
       </c>
       <c r="AY510" t="inlineStr"/>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126079446</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -55777,6 +58327,11 @@
         </is>
       </c>
       <c r="AY511" t="inlineStr"/>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230522</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -55878,6 +58433,11 @@
         </is>
       </c>
       <c r="AY512" t="inlineStr"/>
+      <c r="AZ512" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398377</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -55979,6 +58539,11 @@
         </is>
       </c>
       <c r="AY513" t="inlineStr"/>
+      <c r="AZ513" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230551</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -56080,6 +58645,11 @@
         </is>
       </c>
       <c r="AY514" t="inlineStr"/>
+      <c r="AZ514" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230845</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -56181,6 +58751,11 @@
         </is>
       </c>
       <c r="AY515" t="inlineStr"/>
+      <c r="AZ515" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129192906</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -56282,6 +58857,11 @@
         </is>
       </c>
       <c r="AY516" t="inlineStr"/>
+      <c r="AZ516" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492285</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -56383,6 +58963,11 @@
         </is>
       </c>
       <c r="AY517" t="inlineStr"/>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398996</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -56488,6 +59073,11 @@
         </is>
       </c>
       <c r="AY518" t="inlineStr"/>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126419167</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -56593,6 +59183,11 @@
         </is>
       </c>
       <c r="AY519" t="inlineStr"/>
+      <c r="AZ519" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230833</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -56715,6 +59310,11 @@
         </is>
       </c>
       <c r="AY520" t="inlineStr"/>
+      <c r="AZ520" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859676</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -56818,6 +59418,11 @@
         </is>
       </c>
       <c r="AY521" t="inlineStr"/>
+      <c r="AZ521" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004787</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -56920,6 +59525,11 @@
         </is>
       </c>
       <c r="AY522" t="inlineStr"/>
+      <c r="AZ522" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004770</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -57030,6 +59640,11 @@
         </is>
       </c>
       <c r="AY523" t="inlineStr"/>
+      <c r="AZ523" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212282</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -57136,6 +59751,11 @@
         </is>
       </c>
       <c r="AY524" t="inlineStr"/>
+      <c r="AZ524" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004534</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -57252,6 +59872,11 @@
         </is>
       </c>
       <c r="AY525" t="inlineStr"/>
+      <c r="AZ525" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102873</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -57359,6 +59984,11 @@
         </is>
       </c>
       <c r="AY526" t="inlineStr"/>
+      <c r="AZ526" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744753</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -57461,6 +60091,11 @@
         </is>
       </c>
       <c r="AY527" t="inlineStr"/>
+      <c r="AZ527" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744778</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -57575,6 +60210,11 @@
         </is>
       </c>
       <c r="AY528" t="inlineStr"/>
+      <c r="AZ528" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110687446</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -57694,6 +60334,11 @@
         </is>
       </c>
       <c r="AY529" t="inlineStr"/>
+      <c r="AZ529" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110687528</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -57805,6 +60450,11 @@
         </is>
       </c>
       <c r="AY530" t="inlineStr"/>
+      <c r="AZ530" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386753</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -57906,6 +60556,11 @@
         </is>
       </c>
       <c r="AY531" t="inlineStr"/>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128090410</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -58012,6 +60667,11 @@
         </is>
       </c>
       <c r="AY532" t="inlineStr"/>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342450</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -58122,6 +60782,11 @@
         </is>
       </c>
       <c r="AY533" t="inlineStr"/>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122781209</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -58243,6 +60908,11 @@
         </is>
       </c>
       <c r="AY534" t="inlineStr"/>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949811</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -58369,6 +61039,11 @@
         </is>
       </c>
       <c r="AY535" t="inlineStr"/>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101070100</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -58479,6 +61154,11 @@
         </is>
       </c>
       <c r="AY536" t="inlineStr"/>
+      <c r="AZ536" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124946575</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -58577,6 +61257,11 @@
         </is>
       </c>
       <c r="AY537" t="inlineStr"/>
+      <c r="AZ537" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359756</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -58683,6 +61368,11 @@
         </is>
       </c>
       <c r="AY538" t="inlineStr"/>
+      <c r="AZ538" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102184538</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -58802,6 +61492,11 @@
         </is>
       </c>
       <c r="AY539" t="inlineStr"/>
+      <c r="AZ539" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000431</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -58912,6 +61607,11 @@
         </is>
       </c>
       <c r="AY540" t="inlineStr"/>
+      <c r="AZ540" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359381</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -59013,6 +61713,11 @@
         </is>
       </c>
       <c r="AY541" t="inlineStr"/>
+      <c r="AZ541" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91020696</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -59114,6 +61819,11 @@
         </is>
       </c>
       <c r="AY542" t="inlineStr"/>
+      <c r="AZ542" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91020761</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -59215,6 +61925,11 @@
         </is>
       </c>
       <c r="AY543" t="inlineStr"/>
+      <c r="AZ543" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624772</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -59321,6 +62036,11 @@
         </is>
       </c>
       <c r="AY544" t="inlineStr"/>
+      <c r="AZ544" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646174</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -59427,6 +62147,11 @@
         </is>
       </c>
       <c r="AY545" t="inlineStr"/>
+      <c r="AZ545" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646382</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -59528,6 +62253,11 @@
         </is>
       </c>
       <c r="AY546" t="inlineStr"/>
+      <c r="AZ546" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646693</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -59629,6 +62359,11 @@
         </is>
       </c>
       <c r="AY547" t="inlineStr"/>
+      <c r="AZ547" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646786</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -59730,6 +62465,11 @@
         </is>
       </c>
       <c r="AY548" t="inlineStr"/>
+      <c r="AZ548" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646798</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -59831,6 +62571,11 @@
         </is>
       </c>
       <c r="AY549" t="inlineStr"/>
+      <c r="AZ549" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646840</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -59937,6 +62682,11 @@
         </is>
       </c>
       <c r="AY550" t="inlineStr"/>
+      <c r="AZ550" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646905</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -60038,6 +62788,11 @@
         </is>
       </c>
       <c r="AY551" t="inlineStr"/>
+      <c r="AZ551" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646938</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -60139,6 +62894,11 @@
         </is>
       </c>
       <c r="AY552" t="inlineStr"/>
+      <c r="AZ552" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341675</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -60244,6 +63004,11 @@
         </is>
       </c>
       <c r="AY553" t="inlineStr"/>
+      <c r="AZ553" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338449</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -60345,6 +63110,11 @@
         </is>
       </c>
       <c r="AY554" t="inlineStr"/>
+      <c r="AZ554" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338469</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -60451,6 +63221,11 @@
         </is>
       </c>
       <c r="AY555" t="inlineStr"/>
+      <c r="AZ555" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952470</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -60552,6 +63327,11 @@
         </is>
       </c>
       <c r="AY556" t="inlineStr"/>
+      <c r="AZ556" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338028</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -60653,6 +63433,11 @@
         </is>
       </c>
       <c r="AY557" t="inlineStr"/>
+      <c r="AZ557" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341781</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -60754,6 +63539,11 @@
         </is>
       </c>
       <c r="AY558" t="inlineStr"/>
+      <c r="AZ558" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341797</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -60855,6 +63645,11 @@
         </is>
       </c>
       <c r="AY559" t="inlineStr"/>
+      <c r="AZ559" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112078046</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -60956,6 +63751,11 @@
         </is>
       </c>
       <c r="AY560" t="inlineStr"/>
+      <c r="AZ560" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112078053</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -61057,6 +63857,11 @@
         </is>
       </c>
       <c r="AY561" t="inlineStr"/>
+      <c r="AZ561" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112078061</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -61163,6 +63968,11 @@
         </is>
       </c>
       <c r="AY562" t="inlineStr"/>
+      <c r="AZ562" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341753</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -61269,6 +64079,11 @@
         </is>
       </c>
       <c r="AY563" t="inlineStr"/>
+      <c r="AZ563" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91020564</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -61370,6 +64185,11 @@
         </is>
       </c>
       <c r="AY564" t="inlineStr"/>
+      <c r="AZ564" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91020784</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -61471,6 +64291,11 @@
         </is>
       </c>
       <c r="AY565" t="inlineStr"/>
+      <c r="AZ565" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967605</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -61572,6 +64397,11 @@
         </is>
       </c>
       <c r="AY566" t="inlineStr"/>
+      <c r="AZ566" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645711</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -61673,6 +64503,11 @@
         </is>
       </c>
       <c r="AY567" t="inlineStr"/>
+      <c r="AZ567" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338697</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -61774,6 +64609,11 @@
         </is>
       </c>
       <c r="AY568" t="inlineStr"/>
+      <c r="AZ568" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646597</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -61875,6 +64715,11 @@
         </is>
       </c>
       <c r="AY569" t="inlineStr"/>
+      <c r="AZ569" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96086858</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -61984,6 +64829,11 @@
         </is>
       </c>
       <c r="AY570" t="inlineStr"/>
+      <c r="AZ570" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646657</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -62098,6 +64948,11 @@
         </is>
       </c>
       <c r="AY571" t="inlineStr"/>
+      <c r="AZ571" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779293</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -62207,6 +65062,11 @@
         </is>
       </c>
       <c r="AY572" t="inlineStr"/>
+      <c r="AZ572" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94296112</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -62325,6 +65185,11 @@
         </is>
       </c>
       <c r="AY573" t="inlineStr"/>
+      <c r="AZ573" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125923864</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -62430,6 +65295,11 @@
         </is>
       </c>
       <c r="AY574" t="inlineStr"/>
+      <c r="AZ574" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646606</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -62550,6 +65420,11 @@
         </is>
       </c>
       <c r="AY575" t="inlineStr"/>
+      <c r="AZ575" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692266</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -62652,6 +65527,11 @@
         </is>
       </c>
       <c r="AY576" t="inlineStr"/>
+      <c r="AZ576" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101544040</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -62762,6 +65642,11 @@
         </is>
       </c>
       <c r="AY577" t="inlineStr"/>
+      <c r="AZ577" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126254983</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -62872,6 +65757,11 @@
         </is>
       </c>
       <c r="AY578" t="inlineStr"/>
+      <c r="AZ578" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126255028</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -62973,6 +65863,11 @@
         </is>
       </c>
       <c r="AY579" t="inlineStr"/>
+      <c r="AZ579" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128951711</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -63074,6 +65969,11 @@
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>
+      <c r="AZ580" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91020820</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -63175,6 +66075,11 @@
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
+      <c r="AZ581" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624798</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -63276,6 +66181,11 @@
         </is>
       </c>
       <c r="AY582" t="inlineStr"/>
+      <c r="AZ582" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624833</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -63377,6 +66287,11 @@
         </is>
       </c>
       <c r="AY583" t="inlineStr"/>
+      <c r="AZ583" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624852</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -63478,6 +66393,11 @@
         </is>
       </c>
       <c r="AY584" t="inlineStr"/>
+      <c r="AZ584" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624959</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -63579,6 +66499,11 @@
         </is>
       </c>
       <c r="AY585" t="inlineStr"/>
+      <c r="AZ585" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129625082</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -63680,6 +66605,11 @@
         </is>
       </c>
       <c r="AY586" t="inlineStr"/>
+      <c r="AZ586" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646452</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -63781,6 +66711,11 @@
         </is>
       </c>
       <c r="AY587" t="inlineStr"/>
+      <c r="AZ587" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646495</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -63882,6 +66817,11 @@
         </is>
       </c>
       <c r="AY588" t="inlineStr"/>
+      <c r="AZ588" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646511</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -63983,6 +66923,11 @@
         </is>
       </c>
       <c r="AY589" t="inlineStr"/>
+      <c r="AZ589" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646544</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -64089,6 +67034,11 @@
         </is>
       </c>
       <c r="AY590" t="inlineStr"/>
+      <c r="AZ590" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646621</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -64190,6 +67140,11 @@
         </is>
       </c>
       <c r="AY591" t="inlineStr"/>
+      <c r="AZ591" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129646661</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -64291,6 +67246,11 @@
         </is>
       </c>
       <c r="AY592" t="inlineStr"/>
+      <c r="AZ592" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319679</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -64392,6 +67352,11 @@
         </is>
       </c>
       <c r="AY593" t="inlineStr"/>
+      <c r="AZ593" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319748</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -64493,6 +67458,11 @@
         </is>
       </c>
       <c r="AY594" t="inlineStr"/>
+      <c r="AZ594" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112860776</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -64594,6 +67564,11 @@
         </is>
       </c>
       <c r="AY595" t="inlineStr"/>
+      <c r="AZ595" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128951530</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -64700,6 +67675,11 @@
         </is>
       </c>
       <c r="AY596" t="inlineStr"/>
+      <c r="AZ596" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128951613</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -64806,6 +67786,11 @@
         </is>
       </c>
       <c r="AY597" t="inlineStr"/>
+      <c r="AZ597" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128951955</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -64907,6 +67892,11 @@
         </is>
       </c>
       <c r="AY598" t="inlineStr"/>
+      <c r="AZ598" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338058</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -65008,6 +67998,11 @@
         </is>
       </c>
       <c r="AY599" t="inlineStr"/>
+      <c r="AZ599" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112320337</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -65109,6 +68104,11 @@
         </is>
       </c>
       <c r="AY600" t="inlineStr"/>
+      <c r="AZ600" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338042</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -65210,6 +68210,11 @@
         </is>
       </c>
       <c r="AY601" t="inlineStr"/>
+      <c r="AZ601" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112338376</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -65311,6 +68316,11 @@
         </is>
       </c>
       <c r="AY602" t="inlineStr"/>
+      <c r="AZ602" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128951905</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -65412,6 +68422,11 @@
         </is>
       </c>
       <c r="AY603" t="inlineStr"/>
+      <c r="AZ603" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398172</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -65513,6 +68528,11 @@
         </is>
       </c>
       <c r="AY604" t="inlineStr"/>
+      <c r="AZ604" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398178</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -65614,6 +68634,11 @@
         </is>
       </c>
       <c r="AY605" t="inlineStr"/>
+      <c r="AZ605" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128951446</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -65715,6 +68740,11 @@
         </is>
       </c>
       <c r="AY606" t="inlineStr"/>
+      <c r="AZ606" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128951485</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -65816,6 +68846,11 @@
         </is>
       </c>
       <c r="AY607" t="inlineStr"/>
+      <c r="AZ607" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624807</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -65917,6 +68952,11 @@
         </is>
       </c>
       <c r="AY608" t="inlineStr"/>
+      <c r="AZ608" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128397835</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -66018,6 +69058,11 @@
         </is>
       </c>
       <c r="AY609" t="inlineStr"/>
+      <c r="AZ609" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128397816</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -66119,6 +69164,11 @@
         </is>
       </c>
       <c r="AY610" t="inlineStr"/>
+      <c r="AZ610" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527316</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -66220,6 +69270,11 @@
         </is>
       </c>
       <c r="AY611" t="inlineStr"/>
+      <c r="AZ611" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646591</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -66321,6 +69376,11 @@
         </is>
       </c>
       <c r="AY612" t="inlineStr"/>
+      <c r="AZ612" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319726</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -66435,6 +69495,11 @@
         </is>
       </c>
       <c r="AY613" t="inlineStr"/>
+      <c r="AZ613" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317447</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -66549,6 +69614,11 @@
         </is>
       </c>
       <c r="AY614" t="inlineStr"/>
+      <c r="AZ614" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317586</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -66654,6 +69724,11 @@
         </is>
       </c>
       <c r="AY615" t="inlineStr"/>
+      <c r="AZ615" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624864</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -66768,6 +69843,11 @@
         </is>
       </c>
       <c r="AY616" t="inlineStr"/>
+      <c r="AZ616" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94296292</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -66882,6 +69962,11 @@
         </is>
       </c>
       <c r="AY617" t="inlineStr"/>
+      <c r="AZ617" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123020229</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -66989,6 +70074,11 @@
         </is>
       </c>
       <c r="AY618" t="inlineStr"/>
+      <c r="AZ618" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133768363</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -67103,6 +70193,11 @@
         </is>
       </c>
       <c r="AY619" t="inlineStr"/>
+      <c r="AZ619" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779275</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -67217,6 +70312,11 @@
         </is>
       </c>
       <c r="AY620" t="inlineStr"/>
+      <c r="AZ620" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779278</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -67331,6 +70431,11 @@
         </is>
       </c>
       <c r="AY621" t="inlineStr"/>
+      <c r="AZ621" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779285</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -67441,6 +70546,11 @@
         </is>
       </c>
       <c r="AY622" t="inlineStr"/>
+      <c r="AZ622" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122835034</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -67546,6 +70656,11 @@
         </is>
       </c>
       <c r="AY623" t="inlineStr"/>
+      <c r="AZ623" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341820</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -67651,6 +70766,11 @@
         </is>
       </c>
       <c r="AY624" t="inlineStr"/>
+      <c r="AZ624" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624877</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -67753,6 +70873,11 @@
         </is>
       </c>
       <c r="AY625" t="inlineStr"/>
+      <c r="AZ625" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102043195</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -67855,6 +70980,11 @@
         </is>
       </c>
       <c r="AY626" t="inlineStr"/>
+      <c r="AZ626" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046868</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -67957,6 +71087,11 @@
         </is>
       </c>
       <c r="AY627" t="inlineStr"/>
+      <c r="AZ627" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124537086</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -68058,6 +71193,11 @@
         </is>
       </c>
       <c r="AY628" t="inlineStr"/>
+      <c r="AZ628" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626517</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -68159,6 +71299,11 @@
         </is>
       </c>
       <c r="AY629" t="inlineStr"/>
+      <c r="AZ629" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968206</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -68260,6 +71405,11 @@
         </is>
       </c>
       <c r="AY630" t="inlineStr"/>
+      <c r="AZ630" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887003</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -68361,6 +71511,11 @@
         </is>
       </c>
       <c r="AY631" t="inlineStr"/>
+      <c r="AZ631" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398188</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -68471,6 +71626,11 @@
         </is>
       </c>
       <c r="AY632" t="inlineStr"/>
+      <c r="AZ632" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626241</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -68572,6 +71732,11 @@
         </is>
       </c>
       <c r="AY633" t="inlineStr"/>
+      <c r="AZ633" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527098</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -68674,6 +71839,11 @@
         </is>
       </c>
       <c r="AY634" t="inlineStr"/>
+      <c r="AZ634" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126005083</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -68793,6 +71963,11 @@
         </is>
       </c>
       <c r="AY635" t="inlineStr"/>
+      <c r="AZ635" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110471525</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -68903,6 +72078,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ636" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843531</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -69004,6 +72184,11 @@
         </is>
       </c>
       <c r="AY637" t="inlineStr"/>
+      <c r="AZ637" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314799</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -69110,6 +72295,11 @@
         </is>
       </c>
       <c r="AY638" t="inlineStr"/>
+      <c r="AZ638" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341590</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -69216,6 +72406,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ639" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2006432</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -69322,6 +72517,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ640" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1935408</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -69438,6 +72638,11 @@
         </is>
       </c>
       <c r="AY641" t="inlineStr"/>
+      <c r="AZ641" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94203666</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -69540,6 +72745,11 @@
         </is>
       </c>
       <c r="AY642" t="inlineStr"/>
+      <c r="AZ642" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110471527</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -69659,6 +72869,11 @@
         </is>
       </c>
       <c r="AY643" t="inlineStr"/>
+      <c r="AZ643" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109766771</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -69770,6 +72985,11 @@
         </is>
       </c>
       <c r="AY644" t="inlineStr"/>
+      <c r="AZ644" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94700369</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -69867,6 +73087,11 @@
         </is>
       </c>
       <c r="AY645" t="inlineStr"/>
+      <c r="AZ645" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126409409</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -69982,6 +73207,11 @@
         </is>
       </c>
       <c r="AY646" t="inlineStr"/>
+      <c r="AZ646" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122203249</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -70089,6 +73319,11 @@
         </is>
       </c>
       <c r="AY647" t="inlineStr"/>
+      <c r="AZ647" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122780924</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -70195,6 +73430,11 @@
         </is>
       </c>
       <c r="AY648" t="inlineStr"/>
+      <c r="AZ648" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89855464</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -70296,6 +73536,11 @@
         </is>
       </c>
       <c r="AY649" t="inlineStr"/>
+      <c r="AZ649" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89855499</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -70397,6 +73642,11 @@
         </is>
       </c>
       <c r="AY650" t="inlineStr"/>
+      <c r="AZ650" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129622526</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -70498,6 +73748,11 @@
         </is>
       </c>
       <c r="AY651" t="inlineStr"/>
+      <c r="AZ651" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624048</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -70599,6 +73854,11 @@
         </is>
       </c>
       <c r="AY652" t="inlineStr"/>
+      <c r="AZ652" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624073</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -70700,6 +73960,11 @@
         </is>
       </c>
       <c r="AY653" t="inlineStr"/>
+      <c r="AZ653" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624531</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -70801,6 +74066,11 @@
         </is>
       </c>
       <c r="AY654" t="inlineStr"/>
+      <c r="AZ654" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624559</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -70907,6 +74177,11 @@
         </is>
       </c>
       <c r="AY655" t="inlineStr"/>
+      <c r="AZ655" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624696</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -71008,6 +74283,11 @@
         </is>
       </c>
       <c r="AY656" t="inlineStr"/>
+      <c r="AZ656" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122203275</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -71109,6 +74389,11 @@
         </is>
       </c>
       <c r="AY657" t="inlineStr"/>
+      <c r="AZ657" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952486</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -71210,6 +74495,11 @@
         </is>
       </c>
       <c r="AY658" t="inlineStr"/>
+      <c r="AZ658" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112318671</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -71315,6 +74605,11 @@
         </is>
       </c>
       <c r="AY659" t="inlineStr"/>
+      <c r="AZ659" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358856</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -71424,6 +74719,11 @@
         </is>
       </c>
       <c r="AY660" t="inlineStr"/>
+      <c r="AZ660" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314411</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -71534,6 +74834,11 @@
         </is>
       </c>
       <c r="AY661" t="inlineStr"/>
+      <c r="AZ661" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89855546</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -71635,6 +74940,11 @@
         </is>
       </c>
       <c r="AY662" t="inlineStr"/>
+      <c r="AZ662" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624580</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -71736,6 +75046,11 @@
         </is>
       </c>
       <c r="AY663" t="inlineStr"/>
+      <c r="AZ663" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526460</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -71837,6 +75152,11 @@
         </is>
       </c>
       <c r="AY664" t="inlineStr"/>
+      <c r="AZ664" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314833</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -71938,6 +75258,11 @@
         </is>
       </c>
       <c r="AY665" t="inlineStr"/>
+      <c r="AZ665" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314961</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -72039,6 +75364,11 @@
         </is>
       </c>
       <c r="AY666" t="inlineStr"/>
+      <c r="AZ666" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317789</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -72140,6 +75470,11 @@
         </is>
       </c>
       <c r="AY667" t="inlineStr"/>
+      <c r="AZ667" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526033</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -72241,6 +75576,11 @@
         </is>
       </c>
       <c r="AY668" t="inlineStr"/>
+      <c r="AZ668" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526064</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -72342,6 +75682,11 @@
         </is>
       </c>
       <c r="AY669" t="inlineStr"/>
+      <c r="AZ669" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646583</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -72443,6 +75788,11 @@
         </is>
       </c>
       <c r="AY670" t="inlineStr"/>
+      <c r="AZ670" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112318598</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -72544,6 +75894,11 @@
         </is>
       </c>
       <c r="AY671" t="inlineStr"/>
+      <c r="AZ671" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319943</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -72658,6 +76013,11 @@
         </is>
       </c>
       <c r="AY672" t="inlineStr"/>
+      <c r="AZ672" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128315010</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -72768,6 +76128,11 @@
         </is>
       </c>
       <c r="AY673" t="inlineStr"/>
+      <c r="AZ673" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526198</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -72882,6 +76247,11 @@
         </is>
       </c>
       <c r="AY674" t="inlineStr"/>
+      <c r="AZ674" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624668</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -72991,6 +76361,11 @@
         </is>
       </c>
       <c r="AY675" t="inlineStr"/>
+      <c r="AZ675" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17285491</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -73103,6 +76478,11 @@
         </is>
       </c>
       <c r="AY676" t="inlineStr"/>
+      <c r="AZ676" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79273786</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -73209,6 +76589,11 @@
         </is>
       </c>
       <c r="AY677" t="inlineStr"/>
+      <c r="AZ677" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89840770</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -73315,6 +76700,11 @@
         </is>
       </c>
       <c r="AY678" t="inlineStr"/>
+      <c r="AZ678" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112384453</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -73421,6 +76811,11 @@
         </is>
       </c>
       <c r="AY679" t="inlineStr"/>
+      <c r="AZ679" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122167208</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -73527,6 +76922,11 @@
         </is>
       </c>
       <c r="AY680" t="inlineStr"/>
+      <c r="AZ680" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779297</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -73641,6 +77041,11 @@
         </is>
       </c>
       <c r="AY681" t="inlineStr"/>
+      <c r="AZ681" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779330</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -73746,6 +77151,11 @@
         </is>
       </c>
       <c r="AY682" t="inlineStr"/>
+      <c r="AZ682" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317861</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -73851,6 +77261,11 @@
         </is>
       </c>
       <c r="AY683" t="inlineStr"/>
+      <c r="AZ683" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526054</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -73952,6 +77367,11 @@
         </is>
       </c>
       <c r="AY684" t="inlineStr"/>
+      <c r="AZ684" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967861</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -74059,6 +77479,11 @@
         </is>
       </c>
       <c r="AY685" t="inlineStr"/>
+      <c r="AZ685" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458590</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -74169,8 +77594,700 @@
         </is>
       </c>
       <c r="AY686" t="inlineStr"/>
+      <c r="AZ686" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100478679</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ576" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ577" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ578" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ579" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ580" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ581" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ582" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ583" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ584" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ585" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ586" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ587" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ588" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ589" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ590" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ591" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ592" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ593" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ594" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ595" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ596" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ597" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ598" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ599" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ600" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ601" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ602" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ603" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ604" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ605" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ606" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ607" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ608" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ609" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ610" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ611" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ612" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ613" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ614" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ615" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ616" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ617" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ618" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ619" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ620" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ621" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ622" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ623" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ624" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ625" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ626" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ627" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ628" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ629" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ630" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ631" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ632" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ633" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ634" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ635" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ636" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ637" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ638" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ639" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ640" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ641" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ642" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ643" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ644" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ645" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ646" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ647" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ648" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ649" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ650" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ651" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ652" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ653" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ654" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ655" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ656" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ657" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ658" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ659" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ660" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ661" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ662" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ663" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ664" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ665" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ666" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ667" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ668" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ669" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ670" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ671" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ672" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ673" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ674" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ675" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ676" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ677" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ678" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ679" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ680" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ681" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ682" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ683" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ684" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ685" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ686" r:id="rId685"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -5434,7 +5434,7 @@
         <v>119061006</v>
       </c>
       <c r="B42" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>135075557</v>
       </c>
       <c r="B83" t="n">
-        <v>58061</v>
+        <v>58066</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>135545619</v>
       </c>
       <c r="B91" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>135075195</v>
       </c>
       <c r="B235" t="n">
-        <v>45055</v>
+        <v>45060</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>135074047</v>
       </c>
       <c r="B247" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>135546260</v>
       </c>
       <c r="B320" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>135152950</v>
       </c>
       <c r="B377" t="n">
-        <v>58061</v>
+        <v>58066</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>135359246</v>
       </c>
       <c r="B426" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -60345,7 +60345,7 @@
         <v>135386753</v>
       </c>
       <c r="B530" t="n">
-        <v>107789</v>
+        <v>107844</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>135359756</v>
       </c>
       <c r="B537" t="n">
-        <v>106313</v>
+        <v>106368</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>135359381</v>
       </c>
       <c r="B540" t="n">
-        <v>96629</v>
+        <v>96673</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -74506,7 +74506,7 @@
         <v>135358856</v>
       </c>
       <c r="B659" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -5434,7 +5434,7 @@
         <v>119061006</v>
       </c>
       <c r="B42" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>135545619</v>
       </c>
       <c r="B91" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>135359246</v>
       </c>
       <c r="B426" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -60345,7 +60345,7 @@
         <v>135386753</v>
       </c>
       <c r="B530" t="n">
-        <v>107844</v>
+        <v>107871</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>135359756</v>
       </c>
       <c r="B537" t="n">
-        <v>106368</v>
+        <v>106395</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>135359381</v>
       </c>
       <c r="B540" t="n">
-        <v>96673</v>
+        <v>96700</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -74506,7 +74506,7 @@
         <v>135358856</v>
       </c>
       <c r="B659" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -5434,7 +5434,7 @@
         <v>119061006</v>
       </c>
       <c r="B42" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>135545619</v>
       </c>
       <c r="B91" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>135827249</v>
       </c>
       <c r="B341" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>135359246</v>
       </c>
       <c r="B427" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>135827336</v>
       </c>
       <c r="B514" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>135386753</v>
       </c>
       <c r="B532" t="n">
-        <v>107876</v>
+        <v>107878</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -61379,7 +61379,7 @@
         <v>135359756</v>
       </c>
       <c r="B539" t="n">
-        <v>106400</v>
+        <v>106402</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>135359381</v>
       </c>
       <c r="B542" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -74720,7 +74720,7 @@
         <v>135358856</v>
       </c>
       <c r="B661" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -10932,7 +10932,7 @@
         <v>135545619</v>
       </c>
       <c r="B91" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>135546260</v>
       </c>
       <c r="B320" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>135827212</v>
       </c>
       <c r="B321" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>135827249</v>
       </c>
       <c r="B341" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>135359246</v>
       </c>
       <c r="B427" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>135827336</v>
       </c>
       <c r="B514" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -74720,7 +74720,7 @@
         <v>135358856</v>
       </c>
       <c r="B661" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -10932,7 +10932,7 @@
         <v>135545619</v>
       </c>
       <c r="B91" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>135827249</v>
       </c>
       <c r="B341" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>135359246</v>
       </c>
       <c r="B428" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -59532,7 +59532,7 @@
         <v>135827336</v>
       </c>
       <c r="B523" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -76030,7 +76030,7 @@
         <v>135358856</v>
       </c>
       <c r="B673" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -50766,7 +50766,7 @@
         <v>136193282</v>
       </c>
       <c r="B443" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>136193424</v>
       </c>
       <c r="B444" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -73932,7 +73932,7 @@
         <v>136193016</v>
       </c>
       <c r="B654" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -11044,7 +11044,7 @@
         <v>135545619</v>
       </c>
       <c r="B92" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>136258642</v>
       </c>
       <c r="B101" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>136258592</v>
       </c>
       <c r="B144" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>136258570</v>
       </c>
       <c r="B164" t="n">
-        <v>92745</v>
+        <v>92751</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>136261399</v>
       </c>
       <c r="B249" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>136261113</v>
       </c>
       <c r="B313" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>136260416</v>
       </c>
       <c r="B322" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>135827212</v>
       </c>
       <c r="B328" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>135827249</v>
       </c>
       <c r="B348" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>136159865</v>
       </c>
       <c r="B357" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -49970,7 +49970,7 @@
         <v>135359246</v>
       </c>
       <c r="B435" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>136139193</v>
       </c>
       <c r="B446" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>136159751</v>
       </c>
       <c r="B447" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>136159959</v>
       </c>
       <c r="B448" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>136159979</v>
       </c>
       <c r="B449" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>136193282</v>
       </c>
       <c r="B450" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>136193424</v>
       </c>
       <c r="B451" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>136232449</v>
       </c>
       <c r="B452" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>136259823</v>
       </c>
       <c r="B465" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>136160087</v>
       </c>
       <c r="B471" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>136138429</v>
       </c>
       <c r="B497" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>136138543</v>
       </c>
       <c r="B509" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -58156,7 +58156,7 @@
         <v>136138586</v>
       </c>
       <c r="B510" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -59250,7 +59250,7 @@
         <v>136234180</v>
       </c>
       <c r="B520" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -59352,7 +59352,7 @@
         <v>136234148</v>
       </c>
       <c r="B521" t="n">
-        <v>98161</v>
+        <v>98167</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>135827336</v>
       </c>
       <c r="B538" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -67287,7 +67287,7 @@
         <v>136268106</v>
       </c>
       <c r="B593" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>136138855</v>
       </c>
       <c r="B602" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -68653,7 +68653,7 @@
         <v>136241491</v>
       </c>
       <c r="B605" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -75078,7 +75078,7 @@
         <v>136159945</v>
       </c>
       <c r="B664" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -75419,7 +75419,7 @@
         <v>136226883</v>
       </c>
       <c r="B667" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -75853,7 +75853,7 @@
         <v>136193016</v>
       </c>
       <c r="B671" t="n">
-        <v>91553</v>
+        <v>91559</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -76181,7 +76181,7 @@
         <v>136159708</v>
       </c>
       <c r="B674" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -76291,7 +76291,7 @@
         <v>136239010</v>
       </c>
       <c r="B675" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -78379,7 +78379,7 @@
         <v>135358856</v>
       </c>
       <c r="B694" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -78489,7 +78489,7 @@
         <v>136241603</v>
       </c>
       <c r="B695" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -78606,7 +78606,7 @@
         <v>136231090</v>
       </c>
       <c r="B696" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -78708,7 +78708,7 @@
         <v>136138371</v>
       </c>
       <c r="B697" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -78814,7 +78814,7 @@
         <v>136259499</v>
       </c>
       <c r="B698" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -80572,7 +80572,7 @@
         <v>136241765</v>
       </c>
       <c r="B714" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -81367,7 +81367,7 @@
         <v>136138879</v>
       </c>
       <c r="B721" t="n">
-        <v>57996</v>
+        <v>58000</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -81820,7 +81820,7 @@
         <v>136138971</v>
       </c>
       <c r="B725" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -81930,7 +81930,7 @@
         <v>136193477</v>
       </c>
       <c r="B726" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -7559,7 +7559,7 @@
         <v>136329952</v>
       </c>
       <c r="B61" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136330044</v>
       </c>
       <c r="B62" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>136329900</v>
       </c>
       <c r="B86" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>135545619</v>
       </c>
       <c r="B99" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>136258592</v>
       </c>
       <c r="B152" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>136330155</v>
       </c>
       <c r="B164" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>136330904</v>
       </c>
       <c r="B165" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>136258570</v>
       </c>
       <c r="B174" t="n">
-        <v>92752</v>
+        <v>92758</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>136261399</v>
       </c>
       <c r="B260" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>136261113</v>
       </c>
       <c r="B327" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>136260416</v>
       </c>
       <c r="B336" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>135827249</v>
       </c>
       <c r="B363" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>136159865</v>
       </c>
       <c r="B372" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>135359246</v>
       </c>
       <c r="B450" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>136139193</v>
       </c>
       <c r="B461" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>136159751</v>
       </c>
       <c r="B462" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>136159959</v>
       </c>
       <c r="B463" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>136159979</v>
       </c>
       <c r="B464" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>136193282</v>
       </c>
       <c r="B465" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>136193424</v>
       </c>
       <c r="B466" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>136232449</v>
       </c>
       <c r="B467" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>136259823</v>
       </c>
       <c r="B480" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>136138429</v>
       </c>
       <c r="B512" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60906,7 +60906,7 @@
         <v>136234180</v>
       </c>
       <c r="B535" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>136234148</v>
       </c>
       <c r="B536" t="n">
-        <v>98168</v>
+        <v>98179</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -62873,7 +62873,7 @@
         <v>135827336</v>
       </c>
       <c r="B553" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -68943,7 +68943,7 @@
         <v>136268106</v>
       </c>
       <c r="B608" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -77075,7 +77075,7 @@
         <v>136226883</v>
       </c>
       <c r="B682" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -77509,7 +77509,7 @@
         <v>136193016</v>
       </c>
       <c r="B686" t="n">
-        <v>91560</v>
+        <v>91566</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -80035,7 +80035,7 @@
         <v>135358856</v>
       </c>
       <c r="B709" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -80145,7 +80145,7 @@
         <v>136241603</v>
       </c>
       <c r="B710" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -80262,7 +80262,7 @@
         <v>136231090</v>
       </c>
       <c r="B711" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -80364,7 +80364,7 @@
         <v>136138371</v>
       </c>
       <c r="B712" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -80470,7 +80470,7 @@
         <v>136259499</v>
       </c>
       <c r="B713" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -82228,7 +82228,7 @@
         <v>136241765</v>
       </c>
       <c r="B729" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
